--- a/dcf/COST.xlsx
+++ b/dcf/COST.xlsx
@@ -883,7 +883,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1139,25 +1139,25 @@
         </is>
       </c>
       <c r="B4" s="51" t="n">
-        <v>0.06820114024280483</v>
+        <v>0.06819916692016592</v>
       </c>
       <c r="C4" s="51" t="n">
-        <v>0.07320114024280483</v>
+        <v>0.07319916692016593</v>
       </c>
       <c r="D4" s="51" t="n">
-        <v>0.07820114024280482</v>
+        <v>0.07819916692016592</v>
       </c>
       <c r="E4" s="51" t="n">
-        <v>0.08320114024280482</v>
+        <v>0.08319916692016592</v>
       </c>
       <c r="F4" s="51" t="n">
-        <v>0.08820114024280483</v>
+        <v>0.08819916692016593</v>
       </c>
       <c r="G4" s="51" t="n">
-        <v>0.09320114024280482</v>
+        <v>0.09319916692016592</v>
       </c>
       <c r="H4" s="51" t="n">
-        <v>0.09820114024280482</v>
+        <v>0.09819916692016592</v>
       </c>
     </row>
     <row r="5">
@@ -1165,25 +1165,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>424.5455529986928</v>
+        <v>424.5518232074305</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>409.0353324277685</v>
+        <v>409.041307662731</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>394.2526842352543</v>
+        <v>394.2583799909401</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>380.1594869685464</v>
+        <v>380.1649178506667</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>366.7198006391592</v>
+        <v>366.7249804196675</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>353.8997319796264</v>
+        <v>353.9046736480915</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>341.6673086140082</v>
+        <v>341.6720244256046</v>
       </c>
     </row>
     <row r="6">
@@ -1191,25 +1191,25 @@
         <v>10</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>452.8662100886141</v>
+        <v>452.8730034793584</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>436.0638634917761</v>
+        <v>436.0703357123421</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>420.0536421255015</v>
+        <v>420.0598100948116</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>404.7939223453155</v>
+        <v>404.7998020099774</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>390.2454668797922</v>
+        <v>390.2510732743803</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>376.371277234301</v>
+        <v>376.3766245376268</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>363.1364558683091</v>
+        <v>363.1415574559848</v>
       </c>
     </row>
     <row r="7">
@@ -1217,25 +1217,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>481.1868671785353</v>
+        <v>481.1941837512862</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>463.0923945557838</v>
+        <v>463.0993637619532</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>445.8546000157486</v>
+        <v>445.8612401986831</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>429.4283577220845</v>
+        <v>429.4346861692883</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>413.7711331204251</v>
+        <v>413.7771661290931</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>398.8428224889756</v>
+        <v>398.8485754271622</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>384.60560312261</v>
+        <v>384.611090486365</v>
       </c>
     </row>
     <row r="8">
@@ -1243,25 +1243,25 @@
         <v>12</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>509.5075242684566</v>
+        <v>509.5153640232142</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>490.1209256197914</v>
+        <v>490.1283918115643</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>471.6555579059958</v>
+        <v>471.6626703025546</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>454.0627930988536</v>
+        <v>454.0695703285991</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>437.2967993610582</v>
+        <v>437.303258983806</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>421.3143677436502</v>
+        <v>421.3205263166975</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>406.074750376911</v>
+        <v>406.0806235167452</v>
       </c>
     </row>
     <row r="9">
@@ -1269,25 +1269,25 @@
         <v>13</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>537.8281813583778</v>
+        <v>537.8365442951421</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>517.1494566837989</v>
+        <v>517.1574198611753</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>497.456515796243</v>
+        <v>497.4641004064261</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>478.6972284756227</v>
+        <v>478.70445448791</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>460.8224656016912</v>
+        <v>460.8293518385188</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>443.7859129983248</v>
+        <v>443.7924772062328</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>427.543897631212</v>
+        <v>427.5501565471254</v>
       </c>
     </row>
     <row r="10">
@@ -1295,25 +1295,25 @@
         <v>14</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>566.148838448299</v>
+        <v>566.15772456707</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>544.1779877478066</v>
+        <v>544.1864479107865</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>523.2574736864901</v>
+        <v>523.2655305102976</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>503.3316638523917</v>
+        <v>503.3393386472208</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>484.3481318423243</v>
+        <v>484.3554446932316</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>466.2574582529994</v>
+        <v>466.2644280957682</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>449.013044885513</v>
+        <v>449.0196895775056</v>
       </c>
     </row>
     <row r="11">
@@ -1321,25 +1321,25 @@
         <v>15</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>594.4694955382204</v>
+        <v>594.4789048389978</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>571.2065188118141</v>
+        <v>571.2154759603975</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>549.0584315767373</v>
+        <v>549.0669606141693</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>527.9660992291608</v>
+        <v>527.9742228065317</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>507.8737980829573</v>
+        <v>507.8815375479443</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>488.729003507674</v>
+        <v>488.7363789853035</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>470.4821921398139</v>
+        <v>470.4892226078857</v>
       </c>
     </row>
     <row r="13">
@@ -1349,7 +1349,7 @@
         </is>
       </c>
       <c r="B13" s="53" t="n">
-        <v>951.6699829101562</v>
+        <v>948.7899780273438</v>
       </c>
     </row>
     <row r="14">
@@ -1359,7 +1359,7 @@
         </is>
       </c>
       <c r="B14" s="55" t="n">
-        <v>0.08320114024280482</v>
+        <v>0.08319916692016592</v>
       </c>
       <c r="C14" s="56" t="n">
         <v>12</v>
@@ -1705,7 +1705,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.9655944478238966</v>
+        <v>0.9655944373945814</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24508,7 +24508,7 @@
         </is>
       </c>
       <c r="B48" s="23" t="n">
-        <v>951.6699829101562</v>
+        <v>948.7899780273438</v>
       </c>
     </row>
     <row r="49">
@@ -24670,13 +24670,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>454.0627930988536</v>
+        <v>454.0695703285991</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>844.7993577584973</v>
+        <v>844.8125254848806</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>198.0470308692234</v>
+        <v>198.049753918101</v>
       </c>
     </row>
     <row r="59">
